--- a/dataset/construct/dataset_splits/data_size/2_percent/merged/fold5.xlsx
+++ b/dataset/construct/dataset_splits/data_size/2_percent/merged/fold5.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN5"/>
+  <dimension ref="A1:AK5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,185 +446,170 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>BMI</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>BMI</t>
+          <t>AFPRE</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CABGPRE</t>
+          <t>LVEFPRE</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>AFPRE</t>
+          <t>PREDILATION</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>LVEFPRE</t>
+          <t>CT_ValScNCC</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>NTPROBNPPRE</t>
+          <t>CT_ValScRCC</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>PREDILATION</t>
+          <t>CT_ValScLCC</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScNCC</t>
+          <t>CT_ValvScTot</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScRCC</t>
+          <t>CT_AnnScNCC</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScLCC</t>
+          <t>CT_AnnScRCC</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValvScTot</t>
+          <t>CT_AnnScLCC</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScNCC</t>
+          <t>CT_AnnScTot</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScRCC</t>
+          <t>CT_LVOTScNCC</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScLCC</t>
+          <t>CT_LVOTScRCC</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScTot</t>
+          <t>CT_LVOTScLCC</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScNCC</t>
+          <t>CT_LVOTScTot</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScRCC</t>
+          <t>SEX</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScLCC</t>
+          <t>CT_AnnMean</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScTot</t>
+          <t>ECC_INDEX</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>CT_Peri_Deri</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnMean</t>
+          <t>CT_Area_Deri</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>ECC_INDEX</t>
+          <t>nyha2</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>CT_Peri_Deri</t>
+          <t>nyha3</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>CT_Area_Deri</t>
+          <t>nyha4</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>nyha2</t>
+          <t>model1</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>nyha3</t>
+          <t>model2</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>nyha4</t>
+          <t>model3</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>model1</t>
+          <t>model4</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>model2</t>
+          <t>model7</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>model3</t>
+          <t>model8</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>model4</t>
+          <t>brand2</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>model7</t>
+          <t>brand8</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>model8</t>
+          <t>QRSADM</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>brand2</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>brand8</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>QRSADM</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>PQADM</t>
         </is>
@@ -632,7 +617,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>582</v>
+        <v>481</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -640,85 +625,85 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>84.6962753821583</v>
+        <v>88.08028322812891</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>23.5078053259871</v>
       </c>
       <c r="E2" t="n">
-        <v>24.5351239669421</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>45</v>
+        <v>726</v>
       </c>
       <c r="I2" t="n">
-        <v>3590</v>
+        <v>396</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>285</v>
       </c>
       <c r="K2" t="n">
-        <v>739</v>
+        <v>1407</v>
       </c>
       <c r="L2" t="n">
-        <v>570</v>
+        <v>104</v>
       </c>
       <c r="M2" t="n">
-        <v>485</v>
+        <v>23</v>
       </c>
       <c r="N2" t="n">
-        <v>1794</v>
+        <v>38</v>
       </c>
       <c r="O2" t="n">
-        <v>90</v>
+        <v>165</v>
       </c>
       <c r="P2" t="n">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="Q2" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="R2" t="n">
-        <v>194</v>
+        <v>16</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>22.55</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>22.2816399286988</v>
       </c>
       <c r="X2" t="n">
-        <v>29.85</v>
+        <v>21.6131702613684</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.313559322033898</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>29.921059332824</v>
+        <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>28.8077434310377</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
@@ -739,24 +724,15 @@
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AK2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>638</v>
+        <v>987</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -764,77 +740,79 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>72.7814039090425</v>
+        <v>84.6664857910614</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>26.5118040651432</v>
       </c>
       <c r="E3" t="n">
-        <v>29.7265160523186</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>30</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
+        <v>446</v>
+      </c>
+      <c r="I3" t="n">
+        <v>183</v>
+      </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="K3" t="n">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="L3" t="n">
-        <v>426</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>413</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1514</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>31</v>
+        <v>25.7</v>
       </c>
       <c r="V3" t="n">
-        <v>31</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>25.7830404889228</v>
       </c>
       <c r="X3" t="n">
-        <v>27.1</v>
+        <v>25.4533139190353</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.143835616438356</v>
+        <v>1</v>
       </c>
       <c r="Z3" t="n">
-        <v>27.0562770562771</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>26.7694618135822</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -843,7 +821,7 @@
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
@@ -852,31 +830,24 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="AK3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>116</v>
-      </c>
-      <c r="AN3" t="inlineStr"/>
+        <v>244</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>54108010</v>
+        <v>52234455</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -884,70 +855,82 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>87.4715947980835</v>
+        <v>85.9739904175222</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>29.3333333333333</v>
       </c>
       <c r="E4" t="n">
-        <v>23.4375</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>42</v>
+      </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>66</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
+        <v>259</v>
+      </c>
+      <c r="I4" t="n">
+        <v>204</v>
+      </c>
       <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+        <v>170</v>
+      </c>
+      <c r="K4" t="n">
+        <v>633</v>
+      </c>
+      <c r="L4" t="n">
+        <v>233</v>
+      </c>
+      <c r="M4" t="n">
+        <v>146</v>
+      </c>
+      <c r="N4" t="n">
+        <v>129</v>
+      </c>
       <c r="O4" t="n">
-        <v>120</v>
+        <v>508</v>
       </c>
       <c r="P4" t="n">
-        <v>243</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>197</v>
+        <v>39</v>
       </c>
       <c r="R4" t="n">
-        <v>560</v>
+        <v>258</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>297</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>114</v>
+        <v>25.1</v>
       </c>
       <c r="V4" t="n">
-        <v>114</v>
+        <v>0.23</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>25.49662188332163</v>
       </c>
       <c r="X4" t="n">
-        <v>25.4</v>
+        <v>24.87301941435369</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>81.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>474.2</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -959,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
         <v>0</v>
@@ -971,24 +954,15 @@
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>202</v>
       </c>
       <c r="AK4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>126</v>
+        <v>165</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>51315237</v>
+        <v>53742130</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -996,107 +970,110 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>90.40930869267621</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
+        <v>80.082135523614</v>
+      </c>
+      <c r="D5" t="n">
+        <v>24.3910588392529</v>
+      </c>
       <c r="E5" t="n">
-        <v>29.757785467128</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>57</v>
+      </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>625</v>
+      </c>
+      <c r="I5" t="n">
+        <v>489</v>
+      </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>428</v>
       </c>
       <c r="K5" t="n">
-        <v>556</v>
+        <v>1542</v>
       </c>
       <c r="L5" t="n">
-        <v>486</v>
+        <v>578</v>
       </c>
       <c r="M5" t="n">
-        <v>558</v>
+        <v>375</v>
       </c>
       <c r="N5" t="n">
-        <v>1600</v>
+        <v>337</v>
       </c>
       <c r="O5" t="n">
-        <v>450</v>
+        <v>1290</v>
       </c>
       <c r="P5" t="n">
-        <v>480</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>558</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1488</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>32.9</v>
       </c>
       <c r="V5" t="n">
-        <v>33</v>
+        <v>0.24</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>33.99549584442885</v>
       </c>
       <c r="X5" t="n">
-        <v>28</v>
+        <v>32.75022125856405</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>88.90000000000001</v>
+        <v>1</v>
       </c>
       <c r="AA5" t="n">
-        <v>587.6</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="AK5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
+        <v>120</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
